--- a/output/pdf_financials_xlsx/QZM.xlsx
+++ b/output/pdf_financials_xlsx/QZM.xlsx
@@ -1327,13 +1327,13 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0.106511</v>
+        <v>-0.106511</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0.224103</v>
+        <v>-0.224103</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>0.133639</v>
+        <v>-0.133639</v>
       </c>
       <c r="E16" s="3" t="n">
         <v>-0.174867</v>
@@ -1647,13 +1647,13 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>0.106511</v>
+        <v>-0.106511</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0.224103</v>
+        <v>-0.224103</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>0.133639</v>
+        <v>-0.133639</v>
       </c>
       <c r="E20" s="3" t="n">
         <v>-0.174867</v>
@@ -1836,13 +1836,13 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>0.106511</v>
+        <v>-0.106511</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>0.224103</v>
+        <v>-0.224103</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>0.133639</v>
+        <v>-0.133639</v>
       </c>
       <c r="E23" s="3" t="n">
         <v>-0.174867</v>
@@ -2050,7 +2050,7 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>11.20515</v>
+        <v>-11.20515</v>
       </c>
       <c r="D26" s="1" t="inlineStr">
         <is>
@@ -2114,13 +2114,13 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>0.106511</v>
+        <v>-0.106511</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>0.224103</v>
+        <v>-0.224103</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>0.133639</v>
+        <v>-0.133639</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>-0.174867</v>
@@ -2240,13 +2240,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>0.106511</v>
+        <v>-0.106511</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0.224103</v>
+        <v>-0.224103</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>0.133639</v>
+        <v>-0.133639</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>-0.174867</v>
@@ -2400,13 +2400,13 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
         <v>-0</v>
@@ -6427,49 +6427,49 @@
         <v>0</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>-0.323287</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>-0.331903</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.381139</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.592011</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.592011</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>0.592011</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>0.592011</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>0.592011</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>0.592011</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>0.592011</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>0.592011</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>0.592011</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>0.791151</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>1.432011</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>1.4334</v>
       </c>
       <c r="S92" s="1" t="inlineStr">
         <is>
@@ -10808,7 +10808,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>-</t>
@@ -12472,7 +12476,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E33" t="inlineStr">
         <is>
           <t>-</t>
@@ -15390,7 +15398,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr"/>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E61" t="inlineStr">
         <is>
           <t>-</t>
@@ -17318,7 +17330,11 @@
           <t>Reserves (notes 2 and 7)</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr"/>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E79" t="inlineStr">
         <is>
           <t>-</t>
@@ -18654,7 +18670,11 @@
           <t>Reserves (notes 2 and 7)</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr"/>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E92" t="inlineStr">
         <is>
           <t>-</t>
@@ -58045,13 +58065,13 @@
         </is>
       </c>
       <c r="F473" s="5" t="n">
-        <v>0.224103</v>
+        <v>-0.224103</v>
       </c>
       <c r="G473" s="5" t="n">
-        <v>0.133639</v>
+        <v>-0.133639</v>
       </c>
       <c r="H473" s="5" t="n">
-        <v>0.17468</v>
+        <v>-0.17468</v>
       </c>
       <c r="I473" t="inlineStr">
         <is>
@@ -59302,13 +59322,13 @@
         </is>
       </c>
       <c r="E485" s="5" t="n">
-        <v>0.106511</v>
+        <v>-0.106511</v>
       </c>
       <c r="F485" s="5" t="n">
-        <v>0.224103</v>
+        <v>-0.224103</v>
       </c>
       <c r="G485" s="5" t="n">
-        <v>0.133639</v>
+        <v>-0.133639</v>
       </c>
       <c r="H485" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/QZM.xlsx
+++ b/output/pdf_financials_xlsx/QZM.xlsx
@@ -1075,55 +1075,55 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>-0.024465</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>-0.004451</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>-0.00179</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.001598</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.013067</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.010984</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.009225000000000001</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.01075</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.002971</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.002112</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.002338</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.001846</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.001091</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>0.001376</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>0.003365</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>0.01241</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0</v>
+        <v>0.025089</v>
       </c>
       <c r="S12" s="1" t="inlineStr">
         <is>
@@ -2114,55 +2114,55 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.106511</v>
+        <v>-0.08204599999999999</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.224103</v>
+        <v>-0.219652</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.133639</v>
+        <v>-0.131849</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.174867</v>
+        <v>-0.176465</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-3.587805</v>
+        <v>-3.600872</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-3.458827</v>
+        <v>-3.469811</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-0.8654269999999999</v>
+        <v>-0.874652</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-1.410322</v>
+        <v>-1.421072</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>0.09254900000000001</v>
+        <v>0.089578</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-0.199953</v>
+        <v>-0.202065</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-0.234467</v>
+        <v>-0.236805</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-0.153715</v>
+        <v>-0.155561</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>2.524763</v>
+        <v>2.523672</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-0.152871</v>
+        <v>-0.154247</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-0.913206</v>
+        <v>-0.916571</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-0.910427</v>
+        <v>-0.922837</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>-2.436802</v>
+        <v>-2.461891</v>
       </c>
       <c r="S27" s="1" t="inlineStr">
         <is>
@@ -2240,55 +2240,55 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.106511</v>
+        <v>-0.08204599999999999</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.224103</v>
+        <v>-0.219652</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.133639</v>
+        <v>-0.131849</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.174867</v>
+        <v>-0.176465</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-3.587805</v>
+        <v>-3.600872</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-3.458827</v>
+        <v>-3.469811</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-0.8654269999999999</v>
+        <v>-0.874652</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-1.410322</v>
+        <v>-1.421072</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>0.09254900000000001</v>
+        <v>0.089578</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-0.199953</v>
+        <v>-0.202065</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-0.234467</v>
+        <v>-0.236805</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-0.153715</v>
+        <v>-0.155561</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>2.524763</v>
+        <v>2.523672</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-0.152871</v>
+        <v>-0.154247</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-0.913206</v>
+        <v>-0.916571</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-0.910427</v>
+        <v>-0.922837</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>-2.436802</v>
+        <v>-2.461891</v>
       </c>
       <c r="S29" s="1" t="inlineStr">
         <is>
@@ -2599,25 +2599,25 @@
         <v>0.22591</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.067205</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.07237300000000001</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.206529</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.206443</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.321791</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.097469</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>1.906327</v>
       </c>
       <c r="S34" s="1" t="inlineStr">
         <is>
@@ -2729,25 +2729,25 @@
         <v>0.22591</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.067205</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.07237300000000001</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.206529</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.206443</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.321791</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.097469</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>1.906327</v>
       </c>
       <c r="S36" s="1" t="inlineStr">
         <is>
@@ -3509,25 +3509,25 @@
         <v>0.006242</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.075033</v>
+        <v>0.007828</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.08056099999999999</v>
+        <v>0.008188000000000001</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.218558</v>
+        <v>0.012029</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.211555</v>
+        <v>0.005112</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.340447</v>
+        <v>0.018656</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.12139</v>
+        <v>0.023921</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>2.009669</v>
+        <v>0.103342</v>
       </c>
       <c r="S48" s="1" t="inlineStr">
         <is>
@@ -9440,7 +9440,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -38612,7 +38612,7 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
@@ -38698,7 +38698,7 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
@@ -50058,7 +50058,7 @@
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E397" t="inlineStr">
@@ -50154,7 +50154,7 @@
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E398" t="inlineStr">
@@ -52754,7 +52754,7 @@
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E423" t="inlineStr">
@@ -58582,7 +58582,7 @@
       </c>
       <c r="D478" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E478" s="5" t="n">

--- a/output/pdf_financials_xlsx/QZM.xlsx
+++ b/output/pdf_financials_xlsx/QZM.xlsx
@@ -21294,7 +21294,11 @@
           <t>Proceeds from private placement</t>
         </is>
       </c>
-      <c r="D118" t="inlineStr"/>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E118" t="inlineStr">
         <is>
           <t>-</t>
@@ -24804,7 +24808,11 @@
           <t>Proceeds from private placement 5</t>
         </is>
       </c>
-      <c r="D152" t="inlineStr"/>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E152" t="inlineStr">
         <is>
           <t>-</t>
